--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试点_测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约冲分活动测试点_测试用例.xlsx
@@ -654,7 +654,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>用例来源：薛宇璇_无畏契约冲分活动测试点.xmind    编写人：薛宇璇    编写日期：2026-10-23    用例总数：62    版本：V1.0</t>
+          <t>编写人：薛宇璇    编写日期：2026-10-23    用例总数：62    版本：V1.1</t>
         </is>
       </c>
     </row>
@@ -752,8 +752,7 @@
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>【需提交BUG】活动开启前1秒仍可进入活动，与活动开启时间逻辑不符。
-原脑图：预期“无法进入”、实际“Fail”。</t>
+          <t>【需提交BUG】活动开启前1秒（2025-01-15 23:59:59）仍可进入活动，与活动开启时间逻辑不符。</t>
         </is>
       </c>
     </row>
@@ -804,7 +803,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>活动开启的临界时刻，核心用例。</t>
+          <t>活动开启临界时刻，核心用例。</t>
         </is>
       </c>
     </row>
@@ -885,11 +884,7 @@
 3、观察能否进入活动页面。</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>按原脑图记录为“无法进入”。</t>
-        </is>
-      </c>
+      <c r="F7" s="5" t="inlineStr"/>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>失败（Fail）</t>
@@ -902,7 +897,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>【需确认+可能需提交BUG】原脑图预期结果记为“无法进入”，与“活动结束前应可正常参与”的常规设计逻辑相反，疑似笔误：若预期应为“可进入”，则实际“Fail（无法进入）”需提交BUG。请需求/策划确认后修正预期。</t>
+          <t>【需提交BUG/待确认】活动结束前1秒（2025-01-18 23:59:59）无法进入（实际Fail），与“结束前应可正常参与”的业务逻辑冲突；需先确认预期口径，若预期为可进入则提交BUG。</t>
         </is>
       </c>
     </row>
@@ -931,16 +926,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>1、将时间调整（或等待）至 2025-01-19 00:00:00（原脑图记为“2025年1月18日24点”）；
+          <t>1、将时间调整（或等待）至 2025-01-19 00:00:00；
 2、打开活动中心并点击活动入口；
 3、观察能否进入活动页面。</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>按原脑图记录为“可进入”。</t>
-        </is>
-      </c>
+      <c r="F8" s="5" t="inlineStr"/>
       <c r="G8" s="8" t="inlineStr">
         <is>
           <t>通过（Pass）</t>
@@ -953,7 +944,7 @@
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>原脑图步骤记为“2025年1月18 24点”，等价于 2025-01-19 00:00:00；按脑图预期“可进入”记录，但活动已结束理论上应关闭，需与策划确认边界口径。</t>
+          <t>活动结束时刻即 2025-01-19 00:00:00；活动已结束仍可进入，需与策划确认边界口径。</t>
         </is>
       </c>
     </row>
@@ -987,11 +978,7 @@
 3、观察能否进入活动页面。</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>按原脑图记录为“可进入”。</t>
-        </is>
-      </c>
+      <c r="F9" s="5" t="inlineStr"/>
       <c r="G9" s="8" t="inlineStr">
         <is>
           <t>通过（Pass）</t>
@@ -1004,7 +991,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>同TC-005，活动结束后仍可进入与常规设计逻辑相反，需确认预期口径。</t>
+          <t>活动已结束后仍可进入，与活动关闭逻辑相反，需确认预期口径。</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1020,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>1、将时间调整至活动刷新时间前1秒（原脑图步骤仅标注“边界测试”，建议补足为刷新前1秒的具体时间，如 04:59:59）；
+          <t>1、将时间调整至活动刷新时间前1秒；
 2、打开活动中心并点击活动入口；
 3、观察能否进入活动页面。</t>
         </is>
@@ -1055,7 +1042,7 @@
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>原脑图“实际结果”填写为“无法进入”，与预期一致，已规范为“通过”；步骤缺具体时间点，建议补充。</t>
+          <t>刷新前1秒活动入口暂不可用，与预期一致。</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1071,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>1、将时间调整至活动刷新完成时刻（原脑图步骤为占位符“xxxx”，需补充具体刷新时间点）；
+          <t>1、将时间调整至活动刷新完成时刻；
 2、打开活动中心并点击活动入口；
 3、观察能否进入活动页面及数据是否刷新。</t>
         </is>
@@ -1106,7 +1093,7 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>原脑图操作步骤为占位符“xxxx”，需补充具体时间点后复测确认。</t>
+          <t>刷新完成时刻可正常进入，活动数据已按规则刷新。</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1122,7 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>1、将时间调整至活动刷新后1秒（原脑图步骤仅标注“边界测试”，建议补足为刷新后1秒的具体时间）；
+          <t>1、将时间调整至活动刷新后1秒；
 2、打开活动中心并点击活动入口；
 3、观察能否正常进入。</t>
         </is>
@@ -1157,7 +1144,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>原脑图步骤未写具体时间点，建议补充。</t>
+          <t>刷新后1秒可正常进入。</t>
         </is>
       </c>
     </row>
@@ -1208,8 +1195,7 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>【需提交BUG】9级（未达10级门槛）玩家仍可参与活动，等级门槛校验失效。
-原脑图：预期“不可进入”、实际“Fail”。</t>
+          <t>【需提交BUG】9级（未达10级门槛）玩家仍可参与活动，等级门槛校验失效。</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1344,7 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期结果与实际结果；需产品确认口径后补充预期并执行。</t>
+          <t>未测原因：判定口径待产品确认（建议：达标后可正常参与，无需重新登录）。</t>
         </is>
       </c>
     </row>
@@ -1457,7 +1443,7 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期与实际结果；需产品确认后执行。</t>
+          <t>未测原因：判定口径待产品确认（建议：入口显示但置灰，点击提示“条件不足”）。</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1595,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>文字类，按低档优先级执行；原脑图模块整体标注P2。</t>
+          <t>文字类用例，按低档 P3 执行。</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1692,7 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>临界值-1验证。</t>
+          <t>临界值 -1 验证。</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1794,7 @@
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>原脑图备注“累计完成次数不会每日清空，活动期间可累加”，未给执行结果，需补测跨天累加场景。</t>
+          <t>未测原因：需补测跨天累计（构造第1天3胜 + 第2天3胜）。</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1845,7 @@
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>原脑图未给出执行结果，需补测界面展示与数据一致性。</t>
+          <t>未测原因：需补测剩余次数展示及与活动页面数据一致性。</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1896,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>每日首胜自动消耗加分的核心用例。</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="51.5" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
@@ -1959,7 +1949,7 @@
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列“段位限制：未定级”，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测未定级账号不消耗次数。</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2000,7 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列“段位限制：超凡及以上”，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测超凡及以上账号不消耗次数。</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2052,7 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列前置条件“每日最多加分1次”，未给出执行结果，需补测。</t>
+          <t>未测原因：需补测当日第2次胜利不再消耗次数。</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2101,7 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>时间边界-1秒验证。</t>
+          <t>时间边界 -1 秒验证。</t>
         </is>
       </c>
     </row>
@@ -2160,8 +2150,7 @@
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>时间边界命中验证。
-原脑图“用户体验”建议：周一5点清空加分次数、首胜刷新时间也是5点，建议将活动结束时间同步调整为5点，便于玩家理解与验证。</t>
+          <t>时间边界命中验证。</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2199,7 @@
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>时间边界+1秒验证。</t>
+          <t>时间边界 +1 秒验证。</t>
         </is>
       </c>
     </row>
@@ -2261,7 +2250,7 @@
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期与实际结果，需策划确认口径后执行。</t>
+          <t>未测原因：判定口径待产品确认（建议以结算前段位判定）。</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2301,7 @@
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期与实际结果，需策划确认口径后执行。</t>
+          <t>未测原因：判定口径待产品确认（建议以结算时间计入刷新后当日首胜）。</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2352,7 @@
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期与实际结果，需策划确认口径后执行。</t>
+          <t>未测原因：判定口径待产品确认（建议消极比赛对局不计入任务场次）。</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2401,7 @@
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给出预期与实际结果，需策划确认口径后执行。</t>
+          <t>未测原因：判定口径待产品确认（建议仅可完成一次，不重复发放）。</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2451,7 @@
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>临界值-1验证。</t>
+          <t>临界值 -1 验证。</t>
         </is>
       </c>
     </row>
@@ -2563,7 +2552,7 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>临界值+1验证。</t>
+          <t>临界值 +1 验证。</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2749,7 @@
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列出渠道项，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测主页面点赞的记录写入与渠道标识。</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2799,7 @@
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列出渠道项，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测结算界面点赞的记录写入与渠道标识。</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2849,7 @@
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列出渠道项，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测好友界面点赞的记录写入与渠道标识。</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2899,7 @@
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列出排序方式，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测升序排序结果。</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2949,7 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列出排序方式，未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测降序排序结果。</t>
         </is>
       </c>
     </row>
@@ -3010,7 +2999,7 @@
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>文字格式类，按低档优先级执行；原脑图未给结果。</t>
+          <t>未测原因：需补测时间格式与时区换算（文字类，P3）。</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3049,7 @@
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>文字格式类，按低档优先级执行；原脑图未给结果。</t>
+          <t>未测原因：需补测时间格式与时区换算（文字类，P3）。</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3099,7 @@
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅标注“不清空”，未给执行结果。</t>
+          <t>未测原因：需补测活动结束后记录保留情况。</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3150,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>原脑图未给出预期与实际结果，需补测。</t>
+          <t>未测原因：需补测积分兑换与积分扣除正确性。</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3200,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>原脑图列为前置条件，未给执行结果。</t>
+          <t>未测原因：需补测活动结束后礼包保留与可用性。</t>
         </is>
       </c>
     </row>
@@ -3262,7 +3251,7 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>原脑图“实际结果”为空，未执行。</t>
+          <t>未测原因：需补测礼包开启与随机奖励到账。</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3301,7 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>原脑图列为操作步骤，未给执行结果。</t>
+          <t>未测原因：需补测同种礼包叠加与数量角标。</t>
         </is>
       </c>
     </row>
@@ -3362,7 +3351,7 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>原脑图对6种徽章均标注“概率？”，概率配置与公示值待策划提供后再执行。</t>
+          <t>未测原因：需策划提供 6 种徽章的配置概率后执行概率校验。</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3401,7 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给预期与实际结果，需产品确认后执行。</t>
+          <t>未测原因：需补测背包满时奖励发放（邮箱/临时背包）与提示。</t>
         </is>
       </c>
     </row>
@@ -3462,7 +3451,7 @@
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注“奖励领取在什么位置领取？背包？邮箱？”，需产品确认发放位置后执行。</t>
+          <t>未测原因：待产品确认奖励发放位置（背包/邮箱）后补测。</t>
         </is>
       </c>
     </row>
@@ -3512,7 +3501,7 @@
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给预期与实际结果，需产品确认后执行。</t>
+          <t>未测原因：需补测重复获取多礼包的展示与使用。</t>
         </is>
       </c>
     </row>
@@ -3562,7 +3551,7 @@
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给预期与实际结果，需产品确认后执行。</t>
+          <t>未测原因：待产品确认徽章时效规则后补测。</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3601,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>原脑图标注为“异常”待确认项，未给预期与实际结果，需产品确认后执行。</t>
+          <t>未测原因：需补测并发点赞时记录排序的稳定性。</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3651,7 @@
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>原脑图仅列为前置条件，未给执行结果，需补测。</t>
+          <t>未测原因：需补测红点与实际可领取状态一致性。</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3701,7 @@
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>文字/提示类，按低档优先级执行；原脑图未给执行结果。</t>
+          <t>未测原因：需补测每日首次登录红点提示。</t>
         </is>
       </c>
     </row>
@@ -3760,7 +3749,11 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="I64" s="5" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>红点消除的核心用例。</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="51.5" customHeight="1">
       <c r="A65" s="4" t="inlineStr">
@@ -3808,7 +3801,7 @@
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>原脑图未给出该场景结果，作为红点规则补全用例，需补测。</t>
+          <t>未测原因：需补测无可领取奖励时红点不显示。</t>
         </is>
       </c>
     </row>
@@ -4339,7 +4332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4349,10 +4342,11 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="14" t="inlineStr">
         <is>
-          <t>测试用例要素与填写说明</t>
-        </is>
-      </c>
-    </row>
+          <t>测试用例要素与填写规范</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3" ht="26" customHeight="1">
       <c r="A3" s="25" t="inlineStr">
         <is>
@@ -4365,7 +4359,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="37" customHeight="1">
+    <row r="4" ht="26" customHeight="1">
       <c r="A4" s="25" t="inlineStr">
         <is>
           <t>2. 所属模块</t>
@@ -4373,7 +4367,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>取自脑图一级/二级节点（活动时间、活动参加条件、活动入口、活动界面、双倍加分活动、活动礼包奖励、红点规则），可据此在“测试用例”表筛选。</t>
+          <t>用例归属的功能模块，可按此列筛选执行。</t>
         </is>
       </c>
     </row>
@@ -4385,11 +4379,11 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>一句话说明该用例要验证的功能点，建议“条件 + 对象 + 预期动作”。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="37" customHeight="1">
+          <t>一句话说明要验证的功能点，建议“条件 + 对象 + 预期动作”。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
           <t>4. 前提条件</t>
@@ -4397,11 +4391,11 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>执行该用例前必须准备好的环境、账号、等级、段位、时间、数据等；脑图中“前置条件”节点已全部落入此列。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="37" customHeight="1">
+          <t>执行前必须准备好的环境、账号、等级、段位、时间与数据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
       <c r="A7" s="25" t="inlineStr">
         <is>
           <t>5. 操作步骤</t>
@@ -4409,11 +4403,11 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>按 1/2/3 编号的分步操作，一步一个动作；脑图中所有叶子场景（含边界值、时间点、次数）均已展开为具体步骤。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51.5" customHeight="1">
+          <t>按 1/2/3 分步，一步一个动作；边界值、时间点、次数需写成具体数值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
       <c r="A8" s="25" t="inlineStr">
         <is>
           <t>6. 预期结果</t>
@@ -4421,12 +4415,11 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>依据需求/设计文档应出现的结果，可度量、可判断，避免“正常”“正确”等模糊表述。
-注：脑图中“活动结束时间”相关预期（结束前无法进入、结束时刻可进入）与时间逻辑相反，已在备注标注为待确认项。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="80.5" customHeight="1">
+          <t>依据需求/设计应出现的结果，可度量、可判断，避免“正常”“正确”等模糊表述。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="37" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
           <t>7. 实际结果</t>
@@ -4434,14 +4427,11 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>执行后的真实表现，只填三选一：
-· 通过（Pass）——与预期一致；
-· 失败（Fail）——与预期不一致，需在“备注”写明复现步骤与现象并提交BUG（TC-001、TC-004、TC-010 需提BUG/待确认）；
-· NA（未测）——未执行或当前环境无法测试，必须在“备注”写明原因（缺配置、缺账号、待产品确认等）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51.5" customHeight="1">
+          <t>只填三选一：通过（Pass）＝与预期一致；失败（Fail）＝与预期不一致，需在备注写明现象并提交BUG；NA（未测）＝未执行或当前环境无法测试，必须在备注写明原因。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="37" customHeight="1">
       <c r="A10" s="25" t="inlineStr">
         <is>
           <t>8. 优先级</t>
@@ -4449,12 +4439,11 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>P0 冒烟/核心主流程，阻塞发版；P1 核心功能与关键边界，必测；P2 界面UI、一般功能；P3 文字文案、提示类；P4 极低频边界/体验项。
-按档位对应：低档=文字类（P3）；中档=界面UI类（P2）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="37" customHeight="1">
+          <t>P0 冒烟/主流程，阻塞发版；P1 核心功能与关键边界；P2 界面UI与一般功能；P3 文字文案与提示；P4 极低频边界/体验项。低档对应文字类（P3），中档对应界面UI类（P2）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>9. 备注</t>
@@ -4462,36 +4451,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>记录 BUG 编号、待确认问题、原脑图差异、数据构造方式；本表已将脑图中的“异常”“用户体验”“概率？”等待确认项统一落在此列。</t>
+          <t>仅记录 BUG 编号、未测原因、待确认口径与数据构造方式。</t>
         </is>
       </c>
     </row>
     <row r="12" ht="37" customHeight="1">
-      <c r="A12" s="25" t="inlineStr">
-        <is>
-          <t>数据来源</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>薛宇璇_无畏契约冲分活动测试点.xmind（活动时间/参加条件/入口/界面/双倍加分/礼包奖励/红点规则 共7大模块）。</t>
-        </is>
-      </c>
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="5" t="n"/>
     </row>
     <row r="13" ht="80.5" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
-        <is>
-          <t>落表规则</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>1) 脑图叶子为“预期结果+实际结果”的，按一个用例一行；
-2) 脑图中只写前置条件或占位符（如“xxxx”“边界测试”“s”）的节点，按功能点补全为完整用例；
-3) 脑图标注“异常/待确认”的问题，预期结果写为“待产品确认（建议…）”，实际结果记为 NA 并在备注注明；
-4) 脑图原值一律保留，差异在备注说明，不改写原始执行结论。</t>
-        </is>
-      </c>
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
